--- a/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
+++ b/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
@@ -8,6 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DDR4 command decode" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LPDDR4 CA commands" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Address decode maps" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MR0-MR6 programming maps" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ODT truth table" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FGR refresh select" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -40,7 +45,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -76,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -102,6 +112,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -960,4 +973,1742 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>andesite LPDDR4 CA command contract (pre-RTL, cites MAS pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Contract-style table: command class, 12-bit CA encoding source, and</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>carried fields. Exact CA bit encodings are deliberately not fabricated;</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>they are TBC at the JESD209-4 cold-storage read (HAS Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LPDDR4 CA command placeholder</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/01_cmd_formatter.md:143</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>NOP/ACT/RD/WR/MPC/MRW/MRR/REFab/REFpb are the command classes listed in the MAS placeholder fence. REFpb carries the bank; MPC carries its opcode; MRW carries MR address and data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>CA encoding (12-bit, two-cycle)</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Carries</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>NOP</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>ACT</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Row + bank + bank-group (DDR4-style fields carried to CA mapper)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>RD</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>Bank + column</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>WR</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Bank + column</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>MPC</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>MPC opcode</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>MRW</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>MR address + write data</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>MRR</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>MR address</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>REFab</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>REFpb</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>TBC(JESD209-4)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Bank (controller-directed per-bank refresh)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>andesite address decode maps (pre-RTL, cites MAS pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Field-order table from the address-mapper decode fence and a 2-var</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>K-map of the DDR4 design-point bank-group geometry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Field order by memtype</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/04_addr_mapper.md:77</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Field boundaries are runtime ADDR_MAP-style CSRs, reset to the design-point geometry. LPDDR4 has no bank group; the BG stage is degenerate, not special-cased.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Memtype</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Field order</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>CS -&gt; BG[1:0] -&gt; BA[1:0] -&gt; row -&gt; col</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>Chip select, bank group, bank, row, column</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>CS -&gt; BA[2:0] -&gt; row -&gt; col</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Chip select, bank, row, column (no bank group -- degenerate, not special-cased)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>bg = {BG1, BG0}</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_has/ch02_overview/04_design_point.md:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>bg = {BG1, BG0}   -- DDR4 design-point bank-group decode</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">rows = BG1/BG0   cols = </t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: Each cell is the bank-group number selected by (BG1, BG0); the design point is 4 bank groups x 4 banks = 16 banks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>BG1</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>bank group bit 1</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/04_addr_mapper.md:78</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>BG0</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>bank group bit 0</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/04_addr_mapper.md:78</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: BG1 and BG0. The map is a slice of the DDR4 address path with memtype=DDR4; LPDDR4 has no bank group (BG width = 0).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>BG0</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>BG1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>BG3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>BG2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>andesite MR0-MR6 / LPDDR4 MRW programming maps (pre-RTL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Per-memtype mode-register semantics. Bit positions are named, not</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>numbered; the exact bit maps are confirmed at the JESD79-4 /</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>JESD209-4 cold-storage read (HAS Q1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MR programming map</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/03_mode_register.md:82</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>DDR4 MR0-MR6 are MRS-programmed; LPDDR4 MRs are MRW-programmed over the 6-bit CA bus and read back by MRR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Memtype</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>MR</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Values/notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>MR0</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>Burst length</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Fixed 8 or on-the-fly 4/8</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>MR0</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>Read burst type</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Sequential or interleaved</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>MR0</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>CAS latency</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>CL select</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>MR0</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>DLL reset</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>DLL reset bit</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>MR0</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Write recovery</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>WR select</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>MR1</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="inlineStr">
+        <is>
+          <t>DLL enable</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>DLL on/off</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>MR1</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>Additive latency</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>AL select</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>MR1</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>RTT_NOM</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Nominal termination value</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>MR1</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>Write leveling</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>Write-leveling enable</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>MR2</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>CAS write latency</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>CWL select</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>MR2</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Refresh-related selects</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>FGR-related select bits</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>MR3</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>MPR access/select</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>MPR operation and page select</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="inlineStr">
+        <is>
+          <t>MR3</t>
+        </is>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>FGR select</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>1x / 2x / 4x refresh granularity</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
+        <is>
+          <t>MR3</t>
+        </is>
+      </c>
+      <c r="C23" s="11" t="inlineStr">
+        <is>
+          <t>Gear-down</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="inlineStr">
+        <is>
+          <t>Gear-down mode</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>MR4</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Write CRC mode</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>Inert this edition per HAS Ch 3.1</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>MR4</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>CA parity</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>CA parity latency/mode</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>MR5</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>RD DBI</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>Read DBI enable</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>MR5</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>WR DBI</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Write DBI enable</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>MR5</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>RTT_PARK</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>Idle termination value</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>DDR4</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>MR6</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>VrefDQ</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>VrefDQ training range and value</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>ODT/DQ-ODT</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Termination programming</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Drive strength</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Output driver impedance</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>CA training patterns</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>CA training patterns</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Refresh-related</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Refresh mode bits</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Vendor area</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Vendor-specific MR space</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>andesite ODT termination policy (pre-RTL, cites MAS pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Multi-valued K-map over access type and self/other rank. Mirrors the</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>policy-state fence in the MAS ODT controller page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rtt = odt_policy(access[1:0], self)</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/08_odt_ctrl.md:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>rtt = odt_policy(access[1:0], self)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>rows = access[1]/access[0]   cols = self</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>CHECK BY INSPECTION: IDLE/illegal -&gt; RTT_PARK; read to other rank -&gt; RTT_NOM; read to self -&gt; ODT off; write to self -&gt; RTT_WR; write to other -&gt; RTT_NOM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>AXES</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>axis</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>defining expression</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>cite</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>access[1]</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>MSB of access encoding</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/08_odt_ctrl.md:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>access[0]</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>LSB of access encoding</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/08_odt_ctrl.md:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>command targets this rank</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/08_odt_ctrl.md:88</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>DEPENDS ONLY ON: access[1:0] (idle/read/write) and self. The policy is per-rank; NUM_RANKS &gt; 1 is held in the surrounding structure. Illegal access encoding 11 clamps to PARK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>RTT_PARK</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>RTT_PARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>RTT_NOM</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>ODT off</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>RTT_PARK</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>RTT_PARK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>RTT_NOM</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>RTT_WR</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>andesite FGR refresh select (pre-RTL, cites MAS pages)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>FGR factor from the MR3 image to effective tREFI reload and tRFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>selection. Mirrors the interval-arithmetic fence in the MAS refresh</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>controller page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>FGR refresh select</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/06_refresh_ctrl.md:99</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>The credit-window ceiling (+-8) is unchanged; bookkeeping tracks effective refreshes, not raw commands. Illegal encodings clamp to the 1x row per the MAS/HAS note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>FGR select (MR3 image)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Factor</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>tREFI reload</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>tRFC select</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>1x</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="11" t="inlineStr">
+        <is>
+          <t>tREFI / 1</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>tRFC(1x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" s="11" t="inlineStr">
+        <is>
+          <t>tREFI / 2</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>tRFC(2x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>tREFI / 4</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>tRFC(4x)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>illegal encoding</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>clamp</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>clamped to 1x (tREFI / 1)</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>tRFC(1x)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
+++ b/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
@@ -1504,7 +1504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/03_mode_register.md:82</t>
+          <t>projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/andesite_mas/ch02_blocks/03_mode_register.md:83</t>
         </is>
       </c>
     </row>
@@ -1881,12 +1881,12 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Refresh-related selects</t>
+          <t>RTT_WR</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>FGR-related select bits</t>
+          <t>Write termination value</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>MR3</t>
+          <t>MR2</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>MPR access/select</t>
+          <t>Write CRC mode</t>
         </is>
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>MPR operation and page select</t>
+          <t>Inert this edition per HAS Ch 3.1</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>MR3</t>
+          <t>MR2</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>FGR select</t>
+          <t>LP ASR</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>1x / 2x / 4x refresh granularity</t>
+          <t>Low-power auto self-refresh select</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1962,12 +1962,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>Gear-down</t>
+          <t>MPR access/select</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>Gear-down mode</t>
+          <t>MPR operation and page select</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1984,17 +1984,17 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>MR4</t>
+          <t>MR3</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>Write CRC mode</t>
+          <t>FGR select</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>Inert this edition per HAS Ch 3.1</t>
+          <t>1x / 2x / 4x refresh granularity</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>MR4</t>
+          <t>MR3</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>CA parity</t>
+          <t>Gear-down</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>CA parity latency/mode</t>
+          <t>Gear-down mode</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
@@ -2038,17 +2038,17 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>MR5</t>
+          <t>MR4</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>RD DBI</t>
+          <t>Temperature status</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>Read DBI enable</t>
+          <t>Temperature status</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
@@ -2065,17 +2065,17 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>MR5</t>
+          <t>MR4</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>WR DBI</t>
+          <t>Preamble</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>Write DBI enable</t>
+          <t>Preamble mode</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
@@ -2092,17 +2092,17 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>MR5</t>
+          <t>MR4</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>RTT_PARK</t>
+          <t>CAL</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>Idle termination value</t>
+          <t>Command address latency</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>MR6</t>
+          <t>MR5</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>VrefDQ</t>
+          <t>RD DBI</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>VrefDQ training range and value</t>
+          <t>Read DBI enable</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
@@ -2141,108 +2141,108 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>LPDDR4</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>MRW set</t>
+          <t>MR5</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>ODT/DQ-ODT</t>
+          <t>WR DBI</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>Termination programming</t>
+          <t>Write DBI enable</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>bit map per JESD209-4 (HAS Q1)</t>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>LPDDR4</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>MRW set</t>
+          <t>MR5</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>Drive strength</t>
+          <t>RTT_PARK</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>Output driver impedance</t>
+          <t>Idle termination value</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>bit map per JESD209-4 (HAS Q1)</t>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>LPDDR4</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>MRW set</t>
+          <t>MR5</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>CA training patterns</t>
+          <t>CA parity</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>CA training patterns</t>
+          <t>CA parity latency/mode</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>bit map per JESD209-4 (HAS Q1)</t>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>LPDDR4</t>
+          <t>DDR4</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>MRW set</t>
+          <t>MR6</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>Refresh-related</t>
+          <t>VrefDQ</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>Refresh mode bits</t>
+          <t>VrefDQ training range and value</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>bit map per JESD209-4 (HAS Q1)</t>
+          <t>bit map per JESD79-4 (HAS Q1)</t>
         </is>
       </c>
     </row>
@@ -2259,15 +2259,123 @@
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
+          <t>ODT/DQ-ODT</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>Termination programming</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Drive strength</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>Output driver impedance</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>CA training patterns</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>CA training patterns</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Refresh-related</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>Refresh mode bits</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>bit map per JESD209-4 (HAS Q1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>LPDDR4</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>MRW set</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
           <t>Vendor area</t>
         </is>
       </c>
-      <c r="D34" s="11" t="inlineStr">
+      <c r="D38" s="11" t="inlineStr">
         <is>
           <t>Vendor-specific MR space</t>
         </is>
       </c>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="E38" s="11" t="inlineStr">
         <is>
           <t>bit map per JESD209-4 (HAS Q1)</t>
         </is>

--- a/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
+++ b/projects/components/mem-ctrl-ip/andesite-ddr4-lpddr4/docs/kmaps/andesite_cmd_kmaps.xlsx
@@ -497,7 +497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite DDR4 command decode (pre-RTL, cites MAS pages)</t>
+          <t>andesite DDR4 command decode (citations at the landed RTL; per-command boolean SOP verdicts pending)</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Verdicts on the SOP table are DERIVED, not RTL-diffed -- no RTL exists</t>
+          <t>Verdicts on the SOP table are DERIVED, not RTL-diffed -- the decode is multi-valued;</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite LPDDR4 CA command contract (pre-RTL, cites MAS pages)</t>
+          <t>andesite LPDDR4 CA command contract (encodings TBC(JESD209-4); the DV-repo lpddr4_ca_map from the TASK-010 study is the pending source)</t>
         </is>
       </c>
     </row>
@@ -1025,7 +1025,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+          <t>Verdict posture: per the owning block's RTL phase (P1 landed the formatter/mode_register/init_sequencer).</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite address decode maps (pre-RTL, cites MAS pages)</t>
+          <t>andesite address decode maps (structural map; addr_mapper RTL lands in P3)</t>
         </is>
       </c>
     </row>
@@ -1266,7 +1266,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+          <t>Verdict posture: per the owning block's RTL phase (P1 landed the formatter/mode_register/init_sequencer).</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite MR0-MR6 / LPDDR4 MRW programming maps (pre-RTL)</t>
+          <t>andesite MR0-MR6 / LPDDR4 MRW programming maps (mode_register RTL landed 2026-10-04; bit maps Q1)</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+          <t>Verdict posture: per the owning block's RTL phase (P1 landed the formatter/mode_register/init_sequencer).</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite ODT termination policy (pre-RTL, cites MAS pages)</t>
+          <t>andesite ODT termination policy (odt_ctrl RTL lands in P3)</t>
         </is>
       </c>
     </row>
@@ -2429,7 +2429,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+          <t>Verdict posture: per the owning block's RTL phase (P1 landed the formatter/mode_register/init_sequencer).</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>andesite FGR refresh select (pre-RTL, cites MAS pages)</t>
+          <t>andesite FGR refresh select (refresh_ctrl RTL lands in P3)</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Verdict posture: NOT CHECKED -- no RTL exists at MAS v0.1.</t>
+          <t>Verdict posture: per the owning block's RTL phase (P1 landed the formatter/mode_register/init_sequencer).</t>
         </is>
       </c>
     </row>
